--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="물가" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="고용" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="성장" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="유가" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="금리" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="물가" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="고용" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="성장" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="유가" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="금리" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -3807,7 +3807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4984,6 +4984,21 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -1699,6 +1699,9 @@
       <c r="C61" t="n">
         <v>2.4462</v>
       </c>
+      <c r="D61" t="n">
+        <v>3.0076</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>2026-09-11</t>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -3174,7 +3174,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3797,6 +3797,16 @@
       </c>
       <c r="B61" t="n">
         <v>83.90000000000001</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>97.31</v>
       </c>
     </row>
   </sheetData>
@@ -3810,7 +3820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D78"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4990,13 +5000,28 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B79" t="n">
         <v>4</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -1719,7 +1719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D61"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2824,6 +2824,24 @@
       <c r="D61" t="inlineStr">
         <is>
           <t>2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>159044</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1705,6 +1705,24 @@
       <c r="E61" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>3.7172</v>
+      </c>
+      <c r="C62" t="n">
+        <v>2.5658</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>

--- a/site/data/downloads/usa.xlsx
+++ b/site/data/downloads/usa.xlsx
@@ -1720,6 +1720,9 @@
       <c r="C62" t="n">
         <v>2.5658</v>
       </c>
+      <c r="D62" t="n">
+        <v>3.1212</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -2874,7 +2877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3196,6 +3199,21 @@
       <c r="C21" t="inlineStr">
         <is>
           <t>2026-07-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
